--- a/Data/True_data/current_data/footnotes/ar_aging.xlsx
+++ b/Data/True_data/current_data/footnotes/ar_aging.xlsx
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>146.71</v>
+        <v>110.29</v>
       </c>
     </row>
     <row r="7">
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>60.05</v>
+        <v>52.35</v>
       </c>
     </row>
     <row r="8">
@@ -510,7 +510,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>46.82</v>
+        <v>22.14</v>
       </c>
     </row>
     <row r="9">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>20.93</v>
+        <v>19.47</v>
       </c>
     </row>
     <row r="10">
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>274.51</v>
+        <v>204.26</v>
       </c>
     </row>
     <row r="12">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>-10.11</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="13">
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>264.4</v>
+        <v>201.7</v>
       </c>
     </row>
   </sheetData>
